--- a/Sebastian Nduva - USIU - 265res - 2026/smallholder_access_descriptive_statistics.xlsx
+++ b/Sebastian Nduva - USIU - 265res - 2026/smallholder_access_descriptive_statistics.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.566</v>
+        <v>4.264</v>
       </c>
       <c r="C2" t="n">
-        <v>1.383</v>
+        <v>0.218</v>
       </c>
       <c r="D2" t="n">
-        <v>1.176</v>
+        <v>0.467</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.683</v>
+        <v>4.302</v>
       </c>
       <c r="C3" t="n">
-        <v>1.217</v>
+        <v>0.234</v>
       </c>
       <c r="D3" t="n">
-        <v>1.103</v>
+        <v>0.484</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.517</v>
+        <v>4.343</v>
       </c>
       <c r="C4" t="n">
-        <v>1.364</v>
+        <v>0.249</v>
       </c>
       <c r="D4" t="n">
-        <v>1.168</v>
+        <v>0.499</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.558</v>
+        <v>4.309</v>
       </c>
       <c r="C5" t="n">
-        <v>1.323</v>
+        <v>0.222</v>
       </c>
       <c r="D5" t="n">
-        <v>1.15</v>
+        <v>0.471</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.679</v>
+        <v>4.298</v>
       </c>
       <c r="C6" t="n">
-        <v>1.09</v>
+        <v>0.24</v>
       </c>
       <c r="D6" t="n">
-        <v>1.044</v>
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>
